--- a/制氢成本分析模型.xlsx
+++ b/制氢成本分析模型.xlsx
@@ -1378,48 +1378,38 @@
       </c>
       <c r="C8" s="14" t="inlineStr">
         <is>
-          <t>工业副产氢</t>
+          <t>风电+光伏电解</t>
         </is>
       </c>
       <c r="D8" s="14" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E8" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>AWE</t>
+        </is>
+      </c>
+      <c r="E8" s="14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F8" s="14" t="n">
+        <v>55</v>
+      </c>
+      <c r="G8" s="14" t="n">
+        <v>3100</v>
       </c>
       <c r="H8" s="14" t="n">
-        <v>8000</v>
-      </c>
-      <c r="I8" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J8" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>4200</v>
+      </c>
+      <c r="I8" s="14" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="J8" s="14" t="n">
+        <v>8.5</v>
       </c>
       <c r="K8" s="14" t="n">
-        <v>17.5</v>
+        <v>25</v>
       </c>
       <c r="L8" s="14" t="inlineStr">
         <is>
-          <t>化工副产提纯(PSA) · 管道接收正元氢能 · 蓝氨折氢9.6元/kg</t>
+          <t>风电+光伏电解水 · AWE碱性 · Hebei绿电直供</t>
         </is>
       </c>
     </row>
@@ -1924,12 +1914,12 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>沧州</t>
+          <t>鲁西化工聊城</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>🏭国华</t>
+          <t>⚡竞品</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -1941,7 +1931,7 @@
         <v>17.5</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>8000</v>
+        <v>6000</v>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
@@ -1955,7 +1945,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>鲁西化工聊城</t>
+          <t>中石化库车</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -1965,14 +1955,14 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>工业副产氢</t>
+          <t>光伏电解</t>
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>6000</v>
+        <v>20000</v>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
@@ -1986,7 +1976,7 @@
       </c>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>中石化库车</t>
+          <t>远景赤峰</t>
         </is>
       </c>
       <c r="C29" s="14" t="inlineStr">
@@ -1996,14 +1986,14 @@
       </c>
       <c r="D29" s="14" t="inlineStr">
         <is>
-          <t>光伏电解</t>
+          <t>风电+光伏电解</t>
         </is>
       </c>
       <c r="E29" s="14" t="n">
-        <v>19.5</v>
+        <v>21.3</v>
       </c>
       <c r="F29" s="14" t="n">
-        <v>20000</v>
+        <v>30000</v>
       </c>
       <c r="G29" s="14" t="inlineStr">
         <is>
@@ -2017,7 +2007,7 @@
       </c>
       <c r="B30" s="14" t="inlineStr">
         <is>
-          <t>远景赤峰</t>
+          <t>中石化鄂尔多斯</t>
         </is>
       </c>
       <c r="C30" s="14" t="inlineStr">
@@ -2031,10 +2021,10 @@
         </is>
       </c>
       <c r="E30" s="14" t="n">
-        <v>21.3</v>
+        <v>21.5</v>
       </c>
       <c r="F30" s="14" t="n">
-        <v>30000</v>
+        <v>15000</v>
       </c>
       <c r="G30" s="14" t="inlineStr">
         <is>
@@ -2048,7 +2038,7 @@
       </c>
       <c r="B31" s="14" t="inlineStr">
         <is>
-          <t>中石化鄂尔多斯</t>
+          <t>隆基氢能榆林</t>
         </is>
       </c>
       <c r="C31" s="14" t="inlineStr">
@@ -2058,14 +2048,14 @@
       </c>
       <c r="D31" s="14" t="inlineStr">
         <is>
-          <t>风电+光伏电解</t>
+          <t>光伏电解</t>
         </is>
       </c>
       <c r="E31" s="14" t="n">
-        <v>21.5</v>
+        <v>23</v>
       </c>
       <c r="F31" s="14" t="n">
-        <v>15000</v>
+        <v>3000</v>
       </c>
       <c r="G31" s="14" t="inlineStr">
         <is>
@@ -2079,24 +2069,24 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>隆基氢能榆林</t>
+          <t>沧州</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>⚡竞品</t>
+          <t>🏭国华</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>光伏电解</t>
+          <t>风电+光伏电解</t>
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>3000</v>
+        <v>8000</v>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
@@ -3069,7 +3059,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -3089,7 +3079,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>化工副产提纯(PSA) · 管道接收正元氢能 · 蓝氨折氢9.6元/kg</t>
+          <t>风电+光伏电解水制氢 · AWE碱性电解 · Hebei绿电直供</t>
         </is>
       </c>
     </row>
@@ -3132,7 +3122,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>工业副产氢</t>
+          <t>风电+光伏电解</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3134,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>AWE</t>
         </is>
       </c>
     </row>
@@ -3157,6 +3147,11 @@
       <c r="B9" s="4" t="n">
         <v>8000</v>
       </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>年产能不变</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -3165,7 +3160,12 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>8000</v>
+        <v>4200</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>实际年利用小时</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -3190,17 +3190,17 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>成本项</t>
+          <t>成本参数（电解水制氢）</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>说明</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>金额(元/kg H₂)</t>
+          <t>河北风电+光伏PPA+过网费</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -3217,11 +3217,13 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>正元氢能/聚隆化工副产氢管道直供（原料成本上涨）</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>10</v>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>AWE电解典型值</t>
+        </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
@@ -3237,11 +3239,13 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>变压吸附提纯至99.999%</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v>3.5</v>
+          <t>3100</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>实际采购价·含安装</t>
+        </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
@@ -3257,11 +3261,13 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>管束车充装、人工维护</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>1</v>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>行业典型值</t>
+        </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
@@ -3277,11 +3283,13 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>品质检测、日常管理、认证</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>3</v>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>占Capex比例</t>
+        </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
@@ -3291,8 +3299,16 @@
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr"/>
-      <c r="B20" s="4" t="inlineStr"/>
-      <c r="C20" s="4" t="inlineStr"/>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>水费+耗材+人工</t>
+        </is>
+      </c>
       <c r="D20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
@@ -3311,6 +3327,167 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>成本项</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>计算公式</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>金额(元/kg H₂)</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>① 电力成本</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0.30 × 55</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>66.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>② 折旧</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>3100/(15×4200)×55</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>10.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>③ 固定O&amp;M</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>3100×2.5%/4200×55</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>4.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>④ 水+耗材</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>水+耗材</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>⑤ 人工+运维</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>人工+运维</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>4.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>⑥ 认证+管理+摊销</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>认证+管理费+摊销</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>11.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>◆ 制氢总成本</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>25</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
